--- a/提取和处理/docs/00-规范与记录/实验记录表.xlsx
+++ b/提取和处理/docs/00-规范与记录/实验记录表.xlsx
@@ -1179,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG39"/>
+  <dimension ref="A1:AG42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="4"/>
@@ -7114,6 +7114,459 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A-Opt-07_seed1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>taskA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>xiuyang</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>在 A-Opt-05 母版上对内部节点（is_wall=0）施加 loss 加权（interior_loss_boost=3）是否改善内部流场瓶颈。</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>单变量/对照轴：interior_loss_boost_3（与 experiment_index.csv / run_manifest.json 保持一致）。</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>ae417af</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>coords+t+BC+geometry+is_wall</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>kNN</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>mixedFPS20%</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>center+PCA+scale</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>rotate+translate</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>60</v>
+      </c>
+      <c r="W40" t="n">
+        <v>8</v>
+      </c>
+      <c r="X40" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>106</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>8.958</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>RMSE_|v|</t>
+        </is>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.051712904357069</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>RMSE_p</t>
+        </is>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.6350056975647096</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed1_20260331_175619</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed1_20260331_175619/best_model.pt</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>family=A-Opt-07; study_group=optimization; ablation_axis=interior_loss_boost_3; velocity_R2_detail=见 taskA_field 同 seed 行; source=outputs/field/experiment_index.csv; manifest_notes=与 A-Opt-05 一致，唯一新增 optim.interior_loss_boost=3.0。相对母版未改善主指标（见任务A实验状态表 · A-Opt-07）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A-Opt-07_seed2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>taskA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>xiuyang</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>在 A-Opt-05 母版上对内部节点（is_wall=0）施加 loss 加权（interior_loss_boost=3）是否改善内部流场瓶颈。</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>单变量/对照轴：interior_loss_boost_3（与 experiment_index.csv / run_manifest.json 保持一致）。</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>ae417af</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>2</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>coords+t+BC+geometry+is_wall</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>kNN</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>mixedFPS20%</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>center+PCA+scale</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>rotate+translate</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>60</v>
+      </c>
+      <c r="W41" t="n">
+        <v>8</v>
+      </c>
+      <c r="X41" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>6.098</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>RMSE_|v|</t>
+        </is>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.049976673306081</v>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>RMSE_p</t>
+        </is>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.6683778792594131</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed2_20260331_175619</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed2_20260331_175619/best_model.pt</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>family=A-Opt-07; study_group=optimization; ablation_axis=interior_loss_boost_3; velocity_R2_detail=见 taskA_field 同 seed 行; source=outputs/field/experiment_index.csv; manifest_notes=与 A-Opt-05 一致，唯一新增 optim.interior_loss_boost=3.0。相对母版未改善主指标（见任务A实验状态表 · A-Opt-07）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A-Opt-07_seed3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>taskA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>xiuyang</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>在 A-Opt-05 母版上对内部节点（is_wall=0）施加 loss 加权（interior_loss_boost=3）是否改善内部流场瓶颈。</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>单变量/对照轴：interior_loss_boost_3（与 experiment_index.csv / run_manifest.json 保持一致）。</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>ae417af</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>3</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>coords+t+BC+geometry+is_wall</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>kNN</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>mixedFPS20%</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>center+PCA+scale</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>rotate+translate</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>60</v>
+      </c>
+      <c r="W42" t="n">
+        <v>8</v>
+      </c>
+      <c r="X42" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>72</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>7.211</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>RMSE_|v|</t>
+        </is>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.028344982502139</v>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>RMSE_p</t>
+        </is>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.6432232291687664</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed3_20260331_175619</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed3_20260331_175619/best_model.pt</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>family=A-Opt-07; study_group=optimization; ablation_axis=interior_loss_boost_3; velocity_R2_detail=见 taskA_field 同 seed 行; source=outputs/field/experiment_index.csv; manifest_notes=与 A-Opt-05 一致，唯一新增 optim.interior_loss_boost=3.0。相对母版未改善主指标（见任务A实验状态表 · A-Opt-07）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="B2:B500" showErrorMessage="0" showDropDown="0" showInputMessage="0" allowBlank="1" type="list">
@@ -10823,7 +11276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE39"/>
+  <dimension ref="A1:BE42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17652,6 +18105,513 @@
       <c r="BE39" t="inlineStr">
         <is>
           <t>family=A-Opt-05t_warmup10_wd2e-4; study_group=optimization; ablation_axis=A-Opt-05_optim_warmup10_weight_decay2e-4; ; regional_eval=OK; source=outputs/field/experiment_index.csv; manifest_notes=在 warmup10 基础上仅 weight_decay=2e-4。若明显好再补 seed2/3。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A-Opt-07_seed1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>coords+t+BC+geometry+is_wall</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>kNN</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>mixedFPS20%</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>center+PCA+scale</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>rotate+translate</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>3.035654287193538</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.026153685134134</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.8662300261257777</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.8142992476640438</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.6465883877784047</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.051712904357069</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.6350056975647096</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.4001118427069044</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.9256755113601685</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.2487059235572815</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.3645756840705872</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.6077284812927246</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.05835486948490143</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.844964385032654</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.002622961997986</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.3213512301445007</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.3811285495758057</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.5577020645141602</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.3223555088043213</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.3708516955375671</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0.4910086989402771</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.2833110094070435</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0.4651300311088562</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0.4853450059890747</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0.3128586411476135</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0.4916085600852966</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0.4439495205879211</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>106</v>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>相对 A-Opt-05：全图与 interior 的 RMSE_|v| 未更好，近壁/壁面侧变差；负结果，母版仍为 A-Opt-05（口径见任务A实验状态表）。</t>
+        </is>
+      </c>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed1_20260331_175619/fig_training_curves.png; outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed1_20260331_175619/predictions_test/fig_A3_scatter_interior.png; outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed1_20260331_175619/predictions_test/fig_A4_per_case_boxplot_interior.png; outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed1_20260331_175619/predictions_test/regional_eval/fig_A5_regional_bar_rmse_vel_mag.png; outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed1_20260331_175619/predictions_test/regional_eval/fig_A5_regional_bar_rmse_p.png</t>
+        </is>
+      </c>
+      <c r="BE40" t="inlineStr">
+        <is>
+          <t>family=A-Opt-07; study_group=optimization; ablation_axis=interior_loss_boost_3; regional_eval=OK; source=outputs/field/experiment_index.csv; manifest_notes=与 A-Opt-05 一致，唯一新增 optim.interior_loss_boost=3.0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A-Opt-07_seed2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>coords+t+BC+geometry+is_wall</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>kNN</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>mixedFPS20%</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>center+PCA+scale</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>rotate+translate</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>3.07127169222866</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.024582785174803</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.8793575927623463</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.8213707358362345</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.6506841041424253</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.049976673306081</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.6683778792594131</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.4154174211248285</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.9176580905914307</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.225761890411377</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.3534915447235107</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.6027431488037109</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.07736712694168091</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.806703329086304</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.00707471370697</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.3389346599578857</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.3858984112739563</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.5013987421989441</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.3396806716918945</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0.375377357006073</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0.4286724328994751</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0.2792220711708069</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0.3934123516082764</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0.4120226502418518</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0.1560399532318115</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0.4175155758857727</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0.4313942193984985</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>相对 A-Opt-05：全图与 interior 的 RMSE_|v| 未更好，近壁/壁面侧变差；负结果，母版仍为 A-Opt-05（口径见任务A实验状态表）。</t>
+        </is>
+      </c>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed2_20260331_175619/fig_training_curves.png; outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed2_20260331_175619/predictions_test/fig_A3_scatter_interior.png; outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed2_20260331_175619/predictions_test/fig_A4_per_case_boxplot_interior.png; outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed2_20260331_175619/predictions_test/regional_eval/fig_A5_regional_bar_rmse_vel_mag.png; outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed2_20260331_175619/predictions_test/regional_eval/fig_A5_regional_bar_rmse_p.png</t>
+        </is>
+      </c>
+      <c r="BE41" t="inlineStr">
+        <is>
+          <t>family=A-Opt-07; study_group=optimization; ablation_axis=interior_loss_boost_3; regional_eval=OK; source=outputs/field/experiment_index.csv; manifest_notes=与 A-Opt-05 一致，唯一新增 optim.interior_loss_boost=3.0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A-Opt-07_seed3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>coords+t+BC+geometry+is_wall</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>kNN</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>mixedFPS20%</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>center+PCA+scale</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>rotate+translate</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>3.053637555719894</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.052440399189054</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.8670243801186703</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.8090834060424438</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.6437166317302697</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.028344982502139</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.6432232291687664</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.4122370827617741</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.9237394332885742</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.2473273873329163</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.3726897835731506</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.6112052202224731</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.06505011022090912</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.810440897941589</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.9849916100502014</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.3473232388496399</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.3936982154846191</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0.524674654006958</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.3483944535255432</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0.3831974864006042</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0.4537951350212097</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0.346459686756134</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0.3867828845977783</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0.4537571668624878</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0.2135962247848511</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0.3908562064170837</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0.4783602952957153</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>72</v>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>相对 A-Opt-05：全图与 interior 的 RMSE_|v| 未更好，近壁/壁面侧变差；负结果，母版仍为 A-Opt-05（口径见任务A实验状态表）。</t>
+        </is>
+      </c>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed3_20260331_175619/fig_training_curves.png; outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed3_20260331_175619/predictions_test/fig_A3_scatter_interior.png; outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed3_20260331_175619/predictions_test/fig_A4_per_case_boxplot_interior.png; outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed3_20260331_175619/predictions_test/regional_eval/fig_A5_regional_bar_rmse_vel_mag.png; outputs/field/field_transformer_coord_t_bc_geom_wall_prenorm_tw22205_h256_l4_iboost3_split_AG_v1_seed3_20260331_175619/predictions_test/regional_eval/fig_A5_regional_bar_rmse_p.png</t>
+        </is>
+      </c>
+      <c r="BE42" t="inlineStr">
+        <is>
+          <t>family=A-Opt-07; study_group=optimization; ablation_axis=interior_loss_boost_3; regional_eval=OK; source=outputs/field/experiment_index.csv; manifest_notes=与 A-Opt-05 一致，唯一新增 optim.interior_loss_boost=3.0。</t>
         </is>
       </c>
     </row>

--- a/提取和处理/docs/00-规范与记录/实验记录表.xlsx
+++ b/提取和处理/docs/00-规范与记录/实验记录表.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T123"/>
+  <dimension ref="A1:T130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11930,6 +11930,575 @@
       </c>
       <c r="T123" s="4" t="inlineStr"/>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a_seed1</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>V3P 非对称 WSS 权重 [1,0.05,0.05,0.90]（TODO-6）</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>0.9425</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>157</v>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_a_wall13000_near2000_split_AG_v1_seed1_20260522_124946</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>作业 4957；best_wss test wss_r2_wss=0.399；三 seed 均值 0.394±0.005；+0.029 vs Main-PW</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-WssDO-a_seed1</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-WssDO-a</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>V3P WSS head Dropout=0.15（TODO-7）</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>0.9427</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>100</v>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_wssdo_a_wall13000_near2000_split_AG_v1_seed1_20260522_131813</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>作业 4958；best_wss test wss_r2_wss=0.379；弱于 AsymW</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a_seed2</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>V3P 非对称 WSS 权重 [1,0.05,0.05,0.90]（TODO-6 seed2）</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>2</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>0.9483</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>120</v>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_a_wall13000_near2000_split_AG_v1_seed2_20260523_124511</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>作业 4999；best_wss test wss_r2_wss=0.389；三 seed 均值 0.394±0.005</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a_seed3</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>V3P 非对称 WSS 权重 [1,0.05,0.05,0.90]（TODO-6 seed3）</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>3</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>0.9543</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>142</v>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_a_wall13000_near2000_split_AG_v1_seed3_20260523_124511</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>作业 5000；best_wss test wss_r2_wss=0.395；三 seed 均值 0.394±0.005</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-WssDO-a_seed1</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-WssDO-a</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>AsymW 权重 + wss_head_dropout=0.15 组合（TODO-6+7）</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>0.9434</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>106</v>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_wssdo_a_wall13000_near2000_split_AG_v1_seed1_20260523_124511</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>作业 5001；best_wss test wss_r2_wss=0.398；≈纯 AsymW 0.399，优于单 WssDO 0.379</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>V3D-Probe-P-01_seed1</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>V3D-Probe-P-01</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>V3D 压力探针 post-4901</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>AAA+AG+ILO</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>split_data_new_v3_v3</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>r2_p</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3d_pointnext_localpool_probe_p01_geom_wall13000_near2000_split_data_new_v3_v3_seed1_20260521_103843</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>post-4901 Gate-P ✅ test r2_p=0.984；禁止与 pre-fix 4773 混表</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>V3D-Probe-WSS-01_seed1</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>V3D-Probe-WSS-01</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>V3D WSS 探针 post-4901</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>AAA+AG+ILO</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>split_data_new_v3_v3</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>0.2435</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>12</v>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3d_pointnext_localpool_probe_wss01_geom_wall13000_near2000_split_data_new_v3_v3_seed1_20260521_101738</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>best_wss test wss_r2_wss=0.243；分域 eval 4954</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12016,7 +12585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF123"/>
+  <dimension ref="A1:BF130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -26215,10 +26784,10 @@
         <v>0.42699</v>
       </c>
       <c r="U83" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V83" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W83" s="4" t="n">
         <v>-9.000000000000001e-05</v>
@@ -26245,10 +26814,10 @@
         <v>0.69063</v>
       </c>
       <c r="AK83" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL83" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM83" s="4" t="n">
         <v>-8.000000000000001e-05</v>
@@ -28323,7 +28892,7 @@
         <v>2.34203</v>
       </c>
       <c r="AQ95" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR95" s="4" t="n">
         <v>-0.00455</v>
@@ -28507,7 +29076,7 @@
         <v>2.36814</v>
       </c>
       <c r="AQ96" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR96" s="4" t="n">
         <v>-0.00455</v>
@@ -28691,7 +29260,7 @@
         <v>2.10018</v>
       </c>
       <c r="AQ97" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR97" s="4" t="n">
         <v>-0.00455</v>
@@ -28875,7 +29444,7 @@
         <v>2.31334</v>
       </c>
       <c r="AQ98" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR98" s="4" t="n">
         <v>-0.00455</v>
@@ -29059,7 +29628,7 @@
         <v>2.32893</v>
       </c>
       <c r="AQ99" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR99" s="4" t="n">
         <v>-0.00455</v>
@@ -30057,7 +30626,7 @@
         <v>2.29496</v>
       </c>
       <c r="AQ105" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR105" s="4" t="n">
         <v>-0.00455</v>
@@ -32024,60 +32593,64 @@
         </is>
       </c>
       <c r="N117" s="4" t="n">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="O117" s="4" t="n">
-        <v>0.93292</v>
+        <v>0.9329217891298609</v>
       </c>
       <c r="P117" s="4" t="n">
-        <v>1.10065</v>
+        <v>1.100652872867042</v>
       </c>
       <c r="Q117" s="4" t="n">
-        <v>1.04882</v>
+        <v>1.048822881125274</v>
       </c>
       <c r="R117" s="4" t="n">
-        <v>1.78376</v>
+        <v>1.783762909755492</v>
       </c>
       <c r="S117" s="4" t="n">
-        <v>0.09007</v>
+        <v>0.08097989898100401</v>
       </c>
       <c r="T117" s="4" t="n">
-        <v>0.05256</v>
+        <v>0.04346878479786977</v>
       </c>
       <c r="U117" s="4" t="n">
-        <v>-0.0006400000000000001</v>
+        <v>-0.0006380081176757812</v>
       </c>
       <c r="V117" s="4" t="n">
-        <v>-8.000000000000001e-05</v>
+        <v>-8.153915405273438e-05</v>
       </c>
       <c r="W117" s="4" t="n">
-        <v>-0.00046</v>
+        <v>-0.0004587173461914062</v>
       </c>
       <c r="X117" s="4" t="n">
-        <v>-0.07034</v>
+        <v>-0.07033668188378717</v>
       </c>
       <c r="Y117" s="4" t="n">
-        <v>0.91962</v>
+        <v>0.9350149035453796</v>
       </c>
       <c r="Z117" s="4" t="n">
-        <v>0.3674</v>
+        <v>0.3651911616325378</v>
       </c>
       <c r="AA117" s="4" t="n">
-        <v>0.73149</v>
+        <v>0.7327684836810709</v>
       </c>
       <c r="AB117" s="4" t="n">
-        <v>0.03203</v>
+        <v>0.02231347560882568</v>
       </c>
       <c r="AC117" s="4" t="n">
-        <v>0.02416</v>
+        <v>0.04424643516540527</v>
       </c>
       <c r="AD117" s="4" t="n">
-        <v>0.35886</v>
+        <v>0.3477740883827209</v>
       </c>
       <c r="AE117" s="4" t="n"/>
       <c r="AF117" s="4" t="n"/>
-      <c r="AG117" s="4" t="n"/>
-      <c r="AH117" s="4" t="n"/>
+      <c r="AG117" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH117" s="4" t="n">
+        <v>0.5112418532371521</v>
+      </c>
       <c r="AI117" s="4" t="n">
         <v>1.78376</v>
       </c>
@@ -32138,12 +32711,12 @@
       <c r="BD117" s="4" t="n"/>
       <c r="BE117" s="4" t="inlineStr">
         <is>
-          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_wall13000_near2000_split_AG_v1_seed1_20260506_230831</t>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_wall13000_near2000_split_AG_v1_seed1_20260508_001936</t>
         </is>
       </c>
       <c r="BF117" s="4" t="inlineStr">
         <is>
-          <t>旧run val_score bug，best_epoch=11不可信；已用3634重训（best_epoch=104）</t>
+          <t>3634重训；主报 best_wss wss_r2_wss=0.365</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33620,11 @@
           <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_wall13000_near2000_split_AG_v1_seed1_20260508_001936</t>
         </is>
       </c>
-      <c r="BF122" s="4" t="inlineStr"/>
+      <c r="BF122" s="4" t="inlineStr">
+        <is>
+          <t>重复行（与 row117 同 run）；请仅引用 row117 best_wss 口径 wss=0.365</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -33206,6 +33783,906 @@
         </is>
       </c>
       <c r="BF123" s="4" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a_seed1</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>PointNeXt</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>coords+t+BC+geometry+is_wall</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>157</v>
+      </c>
+      <c r="O124" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P124" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R124" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.05460998132684202</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.03142298777535706</v>
+      </c>
+      <c r="U124" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V124" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W124" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X124" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.9425147771835327</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3989667892456055</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.6943301935449231</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.01815235614776611</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.007309854030609131</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.386707067489624</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.4796649217605591</v>
+      </c>
+      <c r="BE124" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_a_wall13000_near2000_split_AG_v1_seed1_20260522_124946</t>
+        </is>
+      </c>
+      <c r="BF124" t="inlineStr">
+        <is>
+          <t>best_wss test wss_r2_wss=0.399；三 seed 均值 0.394±0.005；+0.029 vs Main-PW</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-WssDO-a_seed1</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-WssDO-a</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>PointNeXt</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>coords+t+BC+geometry+is_wall</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>100</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P125" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R125" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.05453209821044482</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.02993807189542484</v>
+      </c>
+      <c r="U125" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V125" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W125" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X125" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.9426786303520203</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3785686492919922</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.7060141349520983</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.02958565950393677</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.03699380159378052</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3662572503089905</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>57</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.4912031888961792</v>
+      </c>
+      <c r="BE125" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_wssdo_a_wall13000_near2000_split_AG_v1_seed1_20260522_131813</t>
+        </is>
+      </c>
+      <c r="BF125" t="inlineStr">
+        <is>
+          <t>best_wss test wss_r2_wss=0.379；弱于 AsymW</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a_seed2</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>2</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>PointNeXt</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>coords+t+BC+geometry+is_wall</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>120</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P126" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R126" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.05178276014626888</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.03006213386589204</v>
+      </c>
+      <c r="U126" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V126" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W126" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X126" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.9483128190040588</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3890739679336548</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.7000211059556631</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.007644832134246826</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.01003044843673706</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.3762816190719604</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>57</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.5060838460922241</v>
+      </c>
+      <c r="BE126" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_a_wall13000_near2000_split_AG_v1_seed2_20260523_124511</t>
+        </is>
+      </c>
+      <c r="BF126" t="inlineStr">
+        <is>
+          <t>best_wss test wss_r2_wss=0.389；三 seed 均值 0.394±0.005</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a_seed3</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>3</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>PointNeXt</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>coords+t+BC+geometry+is_wall</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>142</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P127" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R127" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.048698771334816</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.02671143185669329</v>
+      </c>
+      <c r="U127" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V127" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.9542860984802246</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3951680064201355</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.696520943162106</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.01549303531646729</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.005058407783508301</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3648107647895813</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>109</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.5117059946060181</v>
+      </c>
+      <c r="BE127" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_a_wall13000_near2000_split_AG_v1_seed3_20260523_124511</t>
+        </is>
+      </c>
+      <c r="BF127" t="inlineStr">
+        <is>
+          <t>best_wss test wss_r2_wss=0.395；三 seed 均值 0.394±0.005</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-WssDO-a_seed1</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-WssDO-a</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>PointNeXt</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>coords+t+BC+geometry+is_wall</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>106</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R128" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.05420101663482306</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.03134985173081578</v>
+      </c>
+      <c r="U128" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V128" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W128" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X128" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.9433725476264954</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3984249830245972</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.6946430805210634</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.03260517120361328</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.0121079683303833</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.3783124685287476</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>53</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.5038925409317017</v>
+      </c>
+      <c r="BE128" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_wssdo_a_wall13000_near2000_split_AG_v1_seed1_20260523_124511</t>
+        </is>
+      </c>
+      <c r="BF128" t="inlineStr">
+        <is>
+          <t>best_wss test wss_r2_wss=0.398；≈纯 AsymW 0.399，优于单 WssDO 0.379</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>V3D-Probe-P-01_seed1</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>V3D-Probe-P-01</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>PointNeXt</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>coords+t+BC+geometry+is_wall</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>split_data_new_v3_v3</t>
+        </is>
+      </c>
+      <c r="O129" t="n">
+        <v>1.09136836031461</v>
+      </c>
+      <c r="P129" t="n">
+        <v>1.039782867787213</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>1.05945477175108</v>
+      </c>
+      <c r="R129" t="n">
+        <v>1.842464924106135</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.1314531420920871</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.05560302818541812</v>
+      </c>
+      <c r="U129" t="n">
+        <v>-1.990795135498047e-05</v>
+      </c>
+      <c r="V129" t="n">
+        <v>-0.0001692771911621094</v>
+      </c>
+      <c r="W129" t="n">
+        <v>-8.916854858398438e-05</v>
+      </c>
+      <c r="X129" t="n">
+        <v>-0.03909671542438931</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.9844526648521423</v>
+      </c>
+      <c r="BE129" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3d_pointnext_localpool_probe_p01_geom_wall13000_near2000_split_data_new_v3_v3_seed1_20260521_103843</t>
+        </is>
+      </c>
+      <c r="BF129" t="inlineStr">
+        <is>
+          <t>post-4901 Gate-P ✅ test r2_p=0.984；禁止与 pre-fix 4773 混表</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>V3D-Probe-WSS-01_seed1</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>V3D-Probe-WSS-01</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>PointNeXt</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>coords+t+BC+geometry+is_wall</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>split_data_new_v3_v3</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>12</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1.141567707365298</v>
+      </c>
+      <c r="P130" t="n">
+        <v>1.074200739537128</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>1.117791740038084</v>
+      </c>
+      <c r="R130" t="n">
+        <v>1.795741309163971</v>
+      </c>
+      <c r="S130" t="n">
+        <v>1.117917489771681</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.6844077335196832</v>
+      </c>
+      <c r="U130" t="n">
+        <v>-0.09413087368011475</v>
+      </c>
+      <c r="V130" t="n">
+        <v>-0.06747841835021973</v>
+      </c>
+      <c r="W130" t="n">
+        <v>-0.1132576465606689</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.01293657189851383</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>-0.1244332790374756</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.2434949278831482</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.9128166255409661</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.02659696340560913</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.03362411260604858</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.1520363688468933</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3355754017829895</v>
+      </c>
+      <c r="BE130" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3d_pointnext_localpool_probe_wss01_geom_wall13000_near2000_split_data_new_v3_v3_seed1_20260521_101738</t>
+        </is>
+      </c>
+      <c r="BF130" t="inlineStr">
+        <is>
+          <t>best_wss test wss_r2_wss=0.243；分域 eval 4954</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/提取和处理/docs/00-规范与记录/实验记录表.xlsx
+++ b/提取和处理/docs/00-规范与记录/实验记录表.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T130"/>
+  <dimension ref="A1:T146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12499,6 +12499,1339 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>V3D-Diag-00_seed1</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>V3D-Diag-00</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>v3d_tri_domain_phase1</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>V3D 三域诊断 smoke（post-fix 口径）</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>AAA+AG+ILO</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>split_data_new_v3</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>1</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0.2061</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>0.9133</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>1</v>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3d_pointnext_localpool_diag00_geom_wall13000_near2000_split_data_new_v3_seed1_20260518_160414</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>V3D 诊断；1 ep smoke，指标不作正式结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>V3P-Probe-WSS-Local-01_seed1</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>V3P-Probe-WSS-Local-01</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>V3P 路径 A：WSS 局部坐标 v1（TODO-5）</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>-1.3834</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>6</v>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_probe_wss_local01_geom_wall13000_near2000_split_AG_v1_seed1_20260525_222125</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>No-Go Track5；best_wss wss=0.411；病例/Pa 未达 Go</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>V3P-Probe-WSS-MagOnly-01_seed1</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>V3P-Probe-WSS-MagOnly-01</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>V3P 路径 A：WSS magnitude-only（TODO-10）</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>-3.7049</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>32</v>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_probe_wss_magonly01_geom_wall13000_near2000_split_AG_v1_seed1_20260526_131051</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>No-Go TODO-10；best_wss wss=0.383</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-GeomB1_seed1</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-GeomB1</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>V3P 路径 B：近壁几何 G01/G04（TODO-12）</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>1</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall_g01_g04</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>0.9421</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>140</v>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_geom_b1_wall13000_near2000_split_AG_v1_seed1_20260526_131204</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>No-Go TODO-12；best_wss wss=0.396</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-VelGradB1_seed1</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-VelGradB1</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>V3P 路径 B：近壁速度梯度上下文（TODO-17）</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall_velgrad_ctx</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>0.9566</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>164</v>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_velgrad_b1_wall13000_near2000_split_AG_v1_seed1_20260527_004949</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>No-Go TODO-17；best_wss wss=0.369</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-MagCons-a_seed1</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-MagCons-a</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>V3P 路径 A：WSS magnitude 一致 loss λ=0.05（TODO-9）</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>0.9241</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>57</v>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_magcons_a_wall13000_near2000_split_AG_v1_seed1_20260527_234624</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>No-Go TODO-9 job 5203；best_wss wss=0.389</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-MagCons-b_seed1</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-MagCons-b</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>V3P 路径 A：WSS magnitude 一致 loss λ=0.10（TODO-9）</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>0.9411</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>108</v>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_magcons_b_wall13000_near2000_split_AG_v1_seed1_20260527_234624</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>No-Go TODO-9 job 5204；best_wss wss=0.390</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>V3P-F-42-Rank1_seed1</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>V3P-F-42-Rank1</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>V3P 路径 F：top10% WSS 排序 loss（TODO-42）</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>0.9459</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>104</v>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_f42_rank1_geom_pw_asymw_wall13000_near2000_split_AG_v1_seed1_20260529_003136</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>No-Go job 5253；best_wss wss=0.378</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>V3P-F-30b-VelConsist_seed1</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>V3P-F-30b-VelConsist</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>V3P 路径 F：WSS↔近壁差分自洽 loss（TODO-30b）</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>7</v>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_f30b_velconsist_wall13000_near2000_split_AG_v1_seed1_20260529_121036</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>No-Go job 5267；best_wss wss=0.321</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>V3P-F-30a-VelSup_seed1</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>V3P-F-30a-VelSup</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>V3P 路径 F：速度监督基线（VelSup，对照 30b/33）</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>1</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>0.9186</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>35</v>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_f30a_velsup_wall13000_near2000_split_AG_v1_seed1_20260529_121036</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>No-Go job 5266；best_wss wss=0.364（速度↑ WSS↓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>V3P-F-33-Slope_seed1</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>V3P-F-33-Slope</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>V3P 路径 F：差分↔GT WSS 斜率监督（TODO-33）</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>0.9261</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>61</v>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_f33_slope_wall13000_near2000_split_AG_v1_seed1_20260529_121036</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>No-Go job 5268；best_wss wss=0.381</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGrad_seed1</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGrad</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>V3P 路径 F：壁面 |∇p| 一致 loss（思路2 loss 版）</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>0.9204</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>140</v>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_fpc_pgrad_wall13000_near2000_split_AG_v1_seed1_20260529_163137</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>No-Go job 5269；best_wss wss=0.395</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>V3P-F-30c-VelDiffInfer_seed1</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>V3P-F-30c-VelDiffInfer</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>V3P 路径 F：vel_diff 结构版（TODO-30c，无 direct head）</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>1</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>0.8878</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>12</v>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_f30c_veldiffinfer_wall13000_near2000_split_AG_v1_seed1_20260530_141452</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>No-Go job 5276；vel_diff 口径 best_wss wss 异常，主报 r2_p</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGradFeat_seed1</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGradFeat</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>V3P 路径 F：|∇p| 拼 wss_head 特征（思路2 输入版）</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>1</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>0.9487</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>104</v>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_fpc_pgradfeat_wall13000_near2000_split_AG_v1_seed1_20260530_141452</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Probe job 5277；best_wss wss=0.406；待三 seed / Pa eval</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>V3D-Probe-WSS-DomainNorm_seed1</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>V3D-Probe-WSS-DomainNorm</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>v3d_tri_domain_phase1</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>V3D TODO-19 per-domain WSS z-score</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>AAA+AG+ILO</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>split_data_new_v3_v3</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0.2461</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>13</v>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3d_pointnext_localpool_probe_wss_domainnorm_wall13000_near2000_split_data_new_v3_v3_seed1_20260530_133250</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>TODO-19 job 5275；best_wss wss=0.246 vs post-4901 0.243</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-MultiK1_seed1</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-MultiK1</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>V3P 路径 B：MultiK 三档 pool（TODO-18）</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>1</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>0.4034</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>0.9245</v>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_multik1_wall13000_near2000_split_AG_v1_seed1_20260527_233948</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>No-Go TODO-18 job 5202；best_wss wss=0.403</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12585,7 +13918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF130"/>
+  <dimension ref="A1:BF146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -34684,6 +36017,2079 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>V3D-Diag-00_seed1</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>V3D-Diag-00</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>split_data_new_v3</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.9905742279267561</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.9852161636129304</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.9213648781050219</v>
+      </c>
+      <c r="R131" t="n">
+        <v>1.419796303713799</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.1185157082235821</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.0554025700753164</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.04846692085266113</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.02580904960632324</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.1645339727401733</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3114520692243701</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.9132672548294067</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.2060584425926208</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.6716441868534182</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.01942133903503418</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.008492529392242432</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.0934409499168396</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3260852098464966</v>
+      </c>
+      <c r="BE131" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3d_pointnext_localpool_diag00_geom_wall13000_near2000_split_data_new_v3_seed1_20260518_160414</t>
+        </is>
+      </c>
+      <c r="BF131" t="inlineStr">
+        <is>
+          <t>V3D 诊断；1 ep smoke，指标不作正式结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>V3P-Probe-WSS-Local-01_seed1</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>V3P-Probe-WSS-Local-01</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>6</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1.066381679431007</v>
+      </c>
+      <c r="P132" t="n">
+        <v>1.131400504859581</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>1.146079801181131</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1.759061815536759</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.5049495757737341</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.4332443476155894</v>
+      </c>
+      <c r="U132" t="n">
+        <v>-0.3074102401733398</v>
+      </c>
+      <c r="V132" t="n">
+        <v>-0.05673813819885254</v>
+      </c>
+      <c r="W132" t="n">
+        <v>-0.1946057081222534</v>
+      </c>
+      <c r="X132" t="n">
+        <v>-0.04089843046091701</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>-1.526709794998169</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.4111639261245728</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.7057363515025833</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.2083666834667199</v>
+      </c>
+      <c r="BE132" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_probe_wss_local01_geom_wall13000_near2000_split_AG_v1_seed1_20260525_222125</t>
+        </is>
+      </c>
+      <c r="BF132" t="inlineStr">
+        <is>
+          <t>No-Go Track5；best_wss wss=0.411；病例/Pa 未达 Go</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>V3P-Probe-WSS-MagOnly-01_seed1</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>V3P-Probe-WSS-MagOnly-01</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>32</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1.262924142798117</v>
+      </c>
+      <c r="P133" t="n">
+        <v>1.346337168574017</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>1.412188599316229</v>
+      </c>
+      <c r="R133" t="n">
+        <v>2.190583765104765</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4512346493646278</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.402138005325587</v>
+      </c>
+      <c r="U133" t="n">
+        <v>-0.09830713272094727</v>
+      </c>
+      <c r="V133" t="n">
+        <v>-0.02554023265838623</v>
+      </c>
+      <c r="W133" t="n">
+        <v>-0.02598881721496582</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.01037478586980156</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>-2.924796342849731</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3827642202377319</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.7036267684821764</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.478478729724884</v>
+      </c>
+      <c r="BE133" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_probe_wss_magonly01_geom_wall13000_near2000_split_AG_v1_seed1_20260526_131051</t>
+        </is>
+      </c>
+      <c r="BF133" t="inlineStr">
+        <is>
+          <t>No-Go TODO-10；best_wss wss=0.383</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-GeomB1_seed1</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-GeomB1</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall_g01_g04</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>140</v>
+      </c>
+      <c r="O134" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P134" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R134" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.04834799238674355</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.0265662672476398</v>
+      </c>
+      <c r="U134" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W134" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X134" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.9549422860145569</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3962163925170898</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.6959170263703898</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.00607222318649292</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.002900063991546631</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3779842257499695</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.487824022769928</v>
+      </c>
+      <c r="BE134" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_geom_b1_wall13000_near2000_split_AG_v1_seed1_20260526_131204</t>
+        </is>
+      </c>
+      <c r="BF134" t="inlineStr">
+        <is>
+          <t>No-Go TODO-12；best_wss wss=0.396</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-VelGradB1_seed1</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-VelGradB1</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall_velgrad_ctx</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>164</v>
+      </c>
+      <c r="O135" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P135" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R135" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.04595434650060062</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.02543514584846284</v>
+      </c>
+      <c r="U135" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V135" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W135" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X135" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.9592933654785156</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.3693874478340149</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.7112104305289365</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.0008265376091003418</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.005059540271759033</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3430954217910767</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.4727844595909119</v>
+      </c>
+      <c r="BE135" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_velgrad_b1_wall13000_near2000_split_AG_v1_seed1_20260527_004949</t>
+        </is>
+      </c>
+      <c r="BF135" t="inlineStr">
+        <is>
+          <t>No-Go TODO-17；best_wss wss=0.369</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-MagCons-a_seed1</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-MagCons-a</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>57</v>
+      </c>
+      <c r="O136" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P136" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R136" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.05089755101759295</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.02880852699104333</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W136" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.9500648975372314</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3889940977096558</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.7000668504970035</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.01263999938964844</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.004409730434417725</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3622393012046814</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.4568747282028198</v>
+      </c>
+      <c r="BE136" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_magcons_a_wall13000_near2000_split_AG_v1_seed1_20260527_234624</t>
+        </is>
+      </c>
+      <c r="BF136" t="inlineStr">
+        <is>
+          <t>No-Go TODO-9 job 5203；best_wss wss=0.389</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-MagCons-b_seed1</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-MagCons-b</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>108</v>
+      </c>
+      <c r="O137" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P137" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R137" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.05227618435577369</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.02776285705640281</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.9473231434822083</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.3904053568840027</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.6992578967484072</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.01010894775390625</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.003956317901611328</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.3763828873634338</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>53</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.4469634890556335</v>
+      </c>
+      <c r="BE137" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_magcons_b_wall13000_near2000_split_AG_v1_seed1_20260527_234624</t>
+        </is>
+      </c>
+      <c r="BF137" t="inlineStr">
+        <is>
+          <t>No-Go TODO-9 job 5204；best_wss wss=0.390</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>V3P-F-42-Rank1_seed1</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>V3P-F-42-Rank1</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>104</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P138" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R138" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.05282084944111968</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.02815182159283466</v>
+      </c>
+      <c r="U138" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V138" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W138" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.9462197422981262</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.378400444984436</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.7061096849884737</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.03136229515075684</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.007768869400024414</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.3758574724197388</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>53</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.4762439131736755</v>
+      </c>
+      <c r="BE138" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_f42_rank1_geom_pw_asymw_wall13000_near2000_split_AG_v1_seed1_20260529_003136</t>
+        </is>
+      </c>
+      <c r="BF138" t="inlineStr">
+        <is>
+          <t>No-Go job 5253；best_wss wss=0.378</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>V3P-F-30b-VelConsist_seed1</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>V3P-F-30b-VelConsist</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>7</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1.1340058238052</v>
+      </c>
+      <c r="P139" t="n">
+        <v>1.186311093741991</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.9943580371656935</v>
+      </c>
+      <c r="R139" t="n">
+        <v>1.473820741398863</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.07472314854735974</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.05247250060518034</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.1144769787788391</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.2037633061408997</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.4913221597671509</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.5520388500615732</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.8923726677894592</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3214042186737061</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.7377723817242774</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.01011013984680176</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.03339338302612305</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3482508063316345</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3912238478660583</v>
+      </c>
+      <c r="BE139" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_f30b_velconsist_wall13000_near2000_split_AG_v1_seed1_20260529_121036</t>
+        </is>
+      </c>
+      <c r="BF139" t="inlineStr">
+        <is>
+          <t>No-Go job 5267；best_wss wss=0.321</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>V3P-F-30a-VelSup_seed1</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>V3P-F-30a-VelSup</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>35</v>
+      </c>
+      <c r="O140" t="n">
+        <v>1.150985222042597</v>
+      </c>
+      <c r="P140" t="n">
+        <v>1.254210203308742</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.9563299289188946</v>
+      </c>
+      <c r="R140" t="n">
+        <v>1.426308436120633</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.05891218978840022</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.03780859658678286</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.08776068687438965</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.1100088953971863</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.529485821723938</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.5804556040786146</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.9331005215644836</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3636326789855957</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.7144482029396374</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.02660858631134033</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.01250773668289185</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3402023911476135</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.4724384546279907</v>
+      </c>
+      <c r="BE140" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_f30a_velsup_wall13000_near2000_split_AG_v1_seed1_20260529_121036</t>
+        </is>
+      </c>
+      <c r="BF140" t="inlineStr">
+        <is>
+          <t>No-Go job 5266；best_wss wss=0.364（速度↑ WSS↓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>V3P-F-33-Slope_seed1</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>V3P-F-33-Slope</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>61</v>
+      </c>
+      <c r="O141" t="n">
+        <v>1.152437598441084</v>
+      </c>
+      <c r="P141" t="n">
+        <v>1.305522671444202</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.9938085258766194</v>
+      </c>
+      <c r="R141" t="n">
+        <v>1.458366813578246</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.05882692985965408</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.03647902444928589</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.0854569673538208</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.03569626808166504</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.4918842315673828</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.5613839004658454</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.9332940578460693</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.3807217478752136</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.7047899853462555</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.01769536733627319</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.02979850769042969</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3503714203834534</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.4500068426132202</v>
+      </c>
+      <c r="BE141" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_f33_slope_wall13000_near2000_split_AG_v1_seed1_20260529_121036</t>
+        </is>
+      </c>
+      <c r="BF141" t="inlineStr">
+        <is>
+          <t>No-Go job 5268；best_wss wss=0.381</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGrad_seed1</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGrad</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>140</v>
+      </c>
+      <c r="O142" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P142" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R142" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.05994205436911412</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.03392012829823288</v>
+      </c>
+      <c r="U142" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V142" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W142" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X142" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.9307411313056946</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3945932984352112</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.696851802784079</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.003844261169433594</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.005476891994476318</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3927875161170959</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>57</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.4821613430976868</v>
+      </c>
+      <c r="BE142" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_fpc_pgrad_wall13000_near2000_split_AG_v1_seed1_20260529_163137</t>
+        </is>
+      </c>
+      <c r="BF142" t="inlineStr">
+        <is>
+          <t>No-Go job 5269；best_wss wss=0.395</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>V3P-F-30c-VelDiffInfer_seed1</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>V3P-F-30c-VelDiffInfer</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>12</v>
+      </c>
+      <c r="O143" t="n">
+        <v>1.107250635575819</v>
+      </c>
+      <c r="P143" t="n">
+        <v>1.188272028595875</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.9655999423198436</v>
+      </c>
+      <c r="R143" t="n">
+        <v>1.505310667925167</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.07627827453754178</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.05239837206487533</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.1557692289352417</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.2011288404464722</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.520319938659668</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.532691908039101</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.8878462314605713</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>256.2282344481612</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>-149961.640625</v>
+      </c>
+      <c r="BE143" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_f30c_veldiffinfer_wall13000_near2000_split_AG_v1_seed1_20260530_141452</t>
+        </is>
+      </c>
+      <c r="BF143" t="inlineStr">
+        <is>
+          <t>No-Go job 5276；vel_diff 口径 best_wss wss 异常，主报 r2_p</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGradFeat_seed1</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGradFeat</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>104</v>
+      </c>
+      <c r="O144" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P144" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R144" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0.05150930769922885</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0.02729677741466957</v>
+      </c>
+      <c r="U144" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V144" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W144" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X144" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0.948857307434082</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>0.4061998128890991</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>0.6901396519971925</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>0.02147960662841797</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>0.005672335624694824</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>0.3784554004669189</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>81</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>0.5023125410079956</v>
+      </c>
+      <c r="BE144" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_fpc_pgradfeat_wall13000_near2000_split_AG_v1_seed1_20260530_141452</t>
+        </is>
+      </c>
+      <c r="BF144" t="inlineStr">
+        <is>
+          <t>Probe job 5277；best_wss wss=0.406；待三 seed / Pa eval</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>V3D-Probe-WSS-DomainNorm_seed1</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>V3D-Probe-WSS-DomainNorm</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>split_data_new_v3_v3</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>13</v>
+      </c>
+      <c r="O145" t="n">
+        <v>1.139376224754507</v>
+      </c>
+      <c r="P145" t="n">
+        <v>1.075308517349813</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>1.155406967816124</v>
+      </c>
+      <c r="R145" t="n">
+        <v>1.814492639861269</v>
+      </c>
+      <c r="S145" t="n">
+        <v>1.049830500371026</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0.6571050547402749</v>
+      </c>
+      <c r="U145" t="n">
+        <v>-0.08993411064147949</v>
+      </c>
+      <c r="V145" t="n">
+        <v>-0.06968116760253906</v>
+      </c>
+      <c r="W145" t="n">
+        <v>-0.1894435882568359</v>
+      </c>
+      <c r="X145" t="n">
+        <v>-0.007785107658759394</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0.00836336612701416</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>0.2461142539978027</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>0.9124772332885617</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>0.01851260662078857</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>0.004139184951782227</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0.1290069222450256</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>0.320193350315094</v>
+      </c>
+      <c r="BE145" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3d_pointnext_localpool_probe_wss_domainnorm_wall13000_near2000_split_data_new_v3_v3_seed1_20260530_133250</t>
+        </is>
+      </c>
+      <c r="BF145" t="inlineStr">
+        <is>
+          <t>TODO-19 job 5275；best_wss wss=0.246 vs post-4901 0.243</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-MultiK1_seed1</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>V3P-Main-01-PW-AsymW-a-MultiK1</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="O146" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P146" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R146" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0.0532448515984229</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0.02878113955458727</v>
+      </c>
+      <c r="U146" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V146" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W146" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X146" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>0.9453528523445129</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>0.403414785861969</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>0.6917561731871351</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>0.0002880692481994629</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>0.008495032787322998</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>0.385915219783783</v>
+      </c>
+      <c r="BE146" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_main01_geom_pw_asymw_multik1_wall13000_near2000_split_AG_v1_seed1_20260527_233948</t>
+        </is>
+      </c>
+      <c r="BF146" t="inlineStr">
+        <is>
+          <t>No-Go TODO-18 job 5202；best_wss wss=0.403</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/提取和处理/docs/00-规范与记录/实验记录表.xlsx
+++ b/提取和处理/docs/00-规范与记录/实验记录表.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T146"/>
+  <dimension ref="A1:T152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13663,7 +13663,7 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>Probe job 5277；best_wss wss=0.406；待三 seed / Pa eval</t>
+          <t>三 seed 0.399±0.010（5277/5300/5301）；未升母版；病例 p95 Spearman 0.551 vs 4957 0.294</t>
         </is>
       </c>
     </row>
@@ -13829,6 +13829,496 @@
       <c r="T146" t="inlineStr">
         <is>
           <t>No-Go TODO-18 job 5202；best_wss wss=0.403</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGradFeat_seed2</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGradFeat</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>V3P 路径 F：|∇p| 拼 wss_head 特征（思路2 输入版）</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>2</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>0.9503</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>148</v>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_fpc_pgradfeat_wall13000_near2000_split_AG_v1_seed2_20260531_224631</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>三 seed 0.399±0.010（5277/5300/5301）；未升母版；病例 p95 Spearman 0.551 vs 4957 0.294</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>V3P-F-Audit-PCv2-BLContext_seed1</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>V3P-F-Audit-PCv2-BLContext</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1_audit</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>V3P 路径 F：PC-v2+BLContext 审计短训（debug 路径）</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>1</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>0.9074</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>2</v>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_audit_pcv2_blctx_wall13000_near2000_split_AG_v1_seed1_20260601_033025</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>审计 job 5303；短训 debug 路径打通；非正式结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGradFeat_seed3</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGradFeat</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>V3P 路径 F：|∇p| 拼 wss_head 特征（思路2 输入版）</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>3</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>0.9527</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>169</v>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_fpc_pgradfeat_wall13000_near2000_split_AG_v1_seed3_20260531_224631</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>三 seed 0.399±0.010（5277/5300/5301）；未升母版；病例 p95 Spearman 0.551 vs 4957 0.294</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>V3P-F-PCv2-BLContext_seed1</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>V3P-F-PCv2-BLContext</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>V3P 路径 F：PC-v2 rich ∇p + naive BL context 正式 Probe</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>1</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>0.9485</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>104</v>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_pcv2_blctx_wall13000_near2000_split_AG_v1_seed1_20260602_145347</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>弱 No-Go job 5311；best_wss wss=0.399≈4957；未超 PGradFeat 0.406</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>V3D-Probe-WSS-Val15_seed1</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>V3D-Probe-WSS-Val15</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>v3d_tri_domain_phase1</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>V3D TODO-3 val15 split Probe（train−14 / val 15%）</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>AAA+AG+ILO</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>split_data_new_v3_val15</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>1</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>R2_p</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>-0.1537</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>12</v>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3d_pointnext_localpool_probe_wss01_val15_geom_wall13000_near2000_split_data_new_v3_val15_seed1_20260603_140618</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>强 No-Go job 5331；best_wss wss=0.039 vs WSS-01 0.243；TODO-3 关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>V3P-F-30c-VelDiffInfer-v2_seed1</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>V3P-F-30c-VelDiffInfer-v2</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>v3_pointcloud_phase1</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>interrupted</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>V3P 路径 F：vel_diff v2 tang_normal 量纲修复 Probe</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>AG_v1</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>1</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>wss_r2_wss</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_f30c_veldiffinfer_v2_wall13000_near2000_split_AG_v1_seed1_20260601_022939</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>作业 5302；强 No-Go job 5302；3 ep 中断无 summary；val_wss_r2≈−1.83；tang_normal 全量长训禁止</t>
         </is>
       </c>
     </row>
@@ -13918,7 +14408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF146"/>
+  <dimension ref="A1:BF152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -37831,7 +38321,7 @@
       </c>
       <c r="BF144" t="inlineStr">
         <is>
-          <t>Probe job 5277；best_wss wss=0.406；待三 seed / Pa eval</t>
+          <t>三 seed 0.399±0.010（5277/5300/5301）；未升母版；病例 p95 Spearman 0.551 vs 4957 0.294</t>
         </is>
       </c>
     </row>
@@ -38087,6 +38577,741 @@
       <c r="BF146" t="inlineStr">
         <is>
           <t>No-Go TODO-18 job 5202；best_wss wss=0.403</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGradFeat_seed2</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGradFeat</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>148</v>
+      </c>
+      <c r="O147" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P147" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R147" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0.04602916258634197</v>
+      </c>
+      <c r="T147" t="n">
+        <v>0.0243653216533527</v>
+      </c>
+      <c r="U147" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V147" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W147" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X147" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>0.9591606855392456</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>0.406222939491272</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>0.6901262000290271</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>0.001710414886474609</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>0.002223193645477295</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0.3822278380393982</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>52</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>0.518506646156311</v>
+      </c>
+      <c r="BE147" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_fpc_pgradfeat_wall13000_near2000_split_AG_v1_seed2_20260531_224631</t>
+        </is>
+      </c>
+      <c r="BF147" t="inlineStr">
+        <is>
+          <t>三 seed 0.399±0.010（5277/5300/5301）；未升母版；病例 p95 Spearman 0.551 vs 4957 0.294</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>V3P-F-Audit-PCv2-BLContext_seed1</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>V3P-F-Audit-PCv2-BLContext</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>2</v>
+      </c>
+      <c r="O148" t="n">
+        <v>1.208126922494874</v>
+      </c>
+      <c r="P148" t="n">
+        <v>1.336456038256842</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>1.394263795813629</v>
+      </c>
+      <c r="R148" t="n">
+        <v>2.242339242786136</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0.08106373310389654</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0.04874976095376422</v>
+      </c>
+      <c r="U148" t="n">
+        <v>-0.005065679550170898</v>
+      </c>
+      <c r="V148" t="n">
+        <v>-0.01054203510284424</v>
+      </c>
+      <c r="W148" t="n">
+        <v>-0.0001084804534912109</v>
+      </c>
+      <c r="X148" t="n">
+        <v>-0.03694007117363141</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>0.8733324408531189</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>0.3772021532058716</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>0.7067899362872934</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>-0.004299521446228027</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>-0.003217220306396484</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>0.3364719748497009</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>0.373480498790741</v>
+      </c>
+      <c r="BE148" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_audit_pcv2_blctx_wall13000_near2000_split_AG_v1_seed1_20260601_033025</t>
+        </is>
+      </c>
+      <c r="BF148" t="inlineStr">
+        <is>
+          <t>审计 job 5303；短训 debug 路径打通；非正式结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGradFeat_seed3</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>V3P-F-PC-PGradFeat</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>3</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>169</v>
+      </c>
+      <c r="O149" t="n">
+        <v>1.205132009973229</v>
+      </c>
+      <c r="P149" t="n">
+        <v>1.329817514231597</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>1.394559126949177</v>
+      </c>
+      <c r="R149" t="n">
+        <v>2.272785338743679</v>
+      </c>
+      <c r="S149" t="n">
+        <v>0.04786108677042133</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0.02548283405954975</v>
+      </c>
+      <c r="U149" t="n">
+        <v>-8.869171142578125e-05</v>
+      </c>
+      <c r="V149" t="n">
+        <v>-0.0005276203155517578</v>
+      </c>
+      <c r="W149" t="n">
+        <v>-0.0005322694778442383</v>
+      </c>
+      <c r="X149" t="n">
+        <v>-0.06529002606700041</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>0.9558452367782593</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>0.3848723769187927</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>0.7024241246554356</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>0.02485471963882446</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>0.005393505096435547</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>0.3598752021789551</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>119</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>0.5322922468185425</v>
+      </c>
+      <c r="BE149" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_fpc_pgradfeat_wall13000_near2000_split_AG_v1_seed3_20260531_224631</t>
+        </is>
+      </c>
+      <c r="BF149" t="inlineStr">
+        <is>
+          <t>三 seed 0.399±0.010（5277/5300/5301）；未升母版；病例 p95 Spearman 0.551 vs 4957 0.294</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>V3P-F-PCv2-BLContext_seed1</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>V3P-F-PCv2-BLContext</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>104</v>
+      </c>
+      <c r="O150" t="n">
+        <v>1.205262607098435</v>
+      </c>
+      <c r="P150" t="n">
+        <v>1.329895713782717</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>1.394252267395241</v>
+      </c>
+      <c r="R150" t="n">
+        <v>2.266263458103349</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0.05173605719316984</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0.02749174534011135</v>
+      </c>
+      <c r="U150" t="n">
+        <v>-0.0003055334091186523</v>
+      </c>
+      <c r="V150" t="n">
+        <v>-0.0006453990936279297</v>
+      </c>
+      <c r="W150" t="n">
+        <v>-9.191036224365234e-05</v>
+      </c>
+      <c r="X150" t="n">
+        <v>-0.05918498316094833</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0.9484060406684875</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>0.3991212248802185</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>0.6942409836251866</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>0.04196947813034058</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>0.008041858673095703</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>0.3744127750396729</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>57</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>0.5026159882545471</v>
+      </c>
+      <c r="BE150" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_pcv2_blctx_wall13000_near2000_split_AG_v1_seed1_20260602_145347</t>
+        </is>
+      </c>
+      <c r="BF150" t="inlineStr">
+        <is>
+          <t>弱 No-Go job 5311；best_wss wss=0.399≈4957；未超 PGradFeat 0.406</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>V3D-Probe-WSS-Val15_seed1</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>V3D-Probe-WSS-Val15</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>mlp2</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>split_data_new_v3_val15</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>12</v>
+      </c>
+      <c r="O151" t="n">
+        <v>1.171265855262461</v>
+      </c>
+      <c r="P151" t="n">
+        <v>1.171555586211124</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>1.120013147269315</v>
+      </c>
+      <c r="R151" t="n">
+        <v>1.868571404533191</v>
+      </c>
+      <c r="S151" t="n">
+        <v>1.152605091118302</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0.6609605387205387</v>
+      </c>
+      <c r="U151" t="n">
+        <v>-0.1749502420425415</v>
+      </c>
+      <c r="V151" t="n">
+        <v>-0.1613483428955078</v>
+      </c>
+      <c r="W151" t="n">
+        <v>-0.101818323135376</v>
+      </c>
+      <c r="X151" t="n">
+        <v>-0.03976838946928285</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>-0.1701126098632812</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>0.03877943754196167</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>1.125636894613565</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>0.01492893695831299</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>-0.05633854866027832</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>0.05492693185806274</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>0.3329850435256958</v>
+      </c>
+      <c r="BE151" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3d_pointnext_localpool_probe_wss01_val15_geom_wall13000_near2000_split_data_new_v3_val15_seed1_20260603_140618</t>
+        </is>
+      </c>
+      <c r="BF151" t="inlineStr">
+        <is>
+          <t>强 No-Go job 5331；best_wss wss=0.039 vs WSS-01 0.243；TODO-3 关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>V3P-F-30c-VelDiffInfer-v2_seed1</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>V3P-F-30c-VelDiffInfer-v2</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>pointnext</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>coord_t_bc_geom_wall</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>vel_diff</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>wall13000_near2000</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>split_AG_v1</t>
+        </is>
+      </c>
+      <c r="BE152" t="inlineStr">
+        <is>
+          <t>outputs/field/field_v3_pointnext_localpool_f30c_veldiffinfer_v2_wall13000_near2000_split_AG_v1_seed1_20260601_022939</t>
+        </is>
+      </c>
+      <c r="BF152" t="inlineStr">
+        <is>
+          <t>作业 5302；强 No-Go job 5302；3 ep 中断无 summary；val_wss_r2≈−1.83；tang_normal 全量长训禁止</t>
         </is>
       </c>
     </row>
